--- a/data/trans_orig/P6903-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6903-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28261</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48423</t>
+          <t>48813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62863</t>
+          <t>62473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83025</t>
+          <t>82852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83087</t>
+          <t>84009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107809</t>
+          <t>108524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72700</t>
+          <t>72330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105755</t>
+          <t>104963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>49960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106645</t>
+          <t>106961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146628</t>
+          <t>148635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181190</t>
+          <t>181982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214245</t>
+          <t>214615</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69472</t>
+          <t>68611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>89468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258887</t>
+          <t>256880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298870</t>
+          <t>298554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48968</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>44170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59261</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40436</t>
+          <t>40175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54591</t>
+          <t>54423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89090</t>
+          <t>89464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111191</t>
+          <t>111516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>129613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170546</t>
+          <t>170683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55237</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83314</t>
+          <t>81376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192224</t>
+          <t>192104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242444</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301759</t>
+          <t>301622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>342692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>138745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164884</t>
+          <t>165202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>449983</t>
+          <t>449530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>500203</t>
+          <t>500323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>20725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60930</t>
+          <t>61525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78530</t>
+          <t>78221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40805</t>
+          <t>40785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67915</t>
+          <t>67819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37493</t>
+          <t>37723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61734</t>
+          <t>60556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86320</t>
+          <t>86490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121476</t>
+          <t>121130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151637</t>
+          <t>151733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178747</t>
+          <t>178767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68688</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92929</t>
+          <t>92699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228498</t>
+          <t>228844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263654</t>
+          <t>263484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29307</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>41526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>38255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77570</t>
+          <t>77477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62209</t>
+          <t>62762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91214</t>
+          <t>93349</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>61476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89027</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132229</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174235</t>
+          <t>173126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>232131</t>
+          <t>229996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261136</t>
+          <t>260583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125651</t>
+          <t>126129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153571</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363788</t>
+          <t>364897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405794</t>
+          <t>407028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>21115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36773</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28793</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46695</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33686</t>
+          <t>34466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71280</t>
+          <t>69499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100770</t>
+          <t>100561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64223</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119230</t>
+          <t>120960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157337</t>
+          <t>157405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128612</t>
+          <t>128821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158102</t>
+          <t>159883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>59815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82404</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196610</t>
+          <t>196542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234717</t>
+          <t>232987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>26859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61648</t>
+          <t>59823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>35496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>53793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75588</t>
+          <t>77413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99702</t>
+          <t>99389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115346</t>
+          <t>115958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152405</t>
+          <t>154128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105873</t>
+          <t>103788</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200880</t>
+          <t>200526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>251239</t>
+          <t>249980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196086</t>
+          <t>194363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>233145</t>
+          <t>232533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>139629</t>
+          <t>142034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313549</t>
+          <t>314808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>363908</t>
+          <t>364262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente agotado a todas horas en 2023 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19791</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62110</t>
+          <t>62442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94072</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104042</t>
+          <t>102442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>123473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184613</t>
+          <t>185928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142858</t>
+          <t>143306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174820</t>
+          <t>174488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134326</t>
+          <t>135926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187368</t>
+          <t>185864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290686</t>
+          <t>289371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351006</t>
+          <t>351826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>32338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80410</t>
+          <t>79495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>33085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>52392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>40849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57456</t>
+          <t>57675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79130</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104809</t>
+          <t>105135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97953</t>
+          <t>97071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135781</t>
+          <t>135224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97629</t>
+          <t>98387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>159419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213549</t>
+          <t>213335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281916</t>
+          <t>285709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199890</t>
+          <t>200447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237718</t>
+          <t>238600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194154</t>
+          <t>193948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255738</t>
+          <t>254980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407122</t>
+          <t>403329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475489</t>
+          <t>475703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
